--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>132061204</v>
       </c>
       <c r="B3" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>132061204</v>
       </c>
       <c r="B3" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,543 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132217153</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Simontorp, Vanderydvattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>342632</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6441273</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132217338</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97913</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora Grankärr, Stora Grankärr, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>342425</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6440968</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vid kanten av impediment mot vägen...</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132214876</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sköljeberget, Sköljeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>342641</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6441071</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På död björk i kanten av dråg</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132216998</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97913</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Simontorp, Simontorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>342632</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6441273</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132214000</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97919</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sköljeberget, Sköljeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>342641</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6441071</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132217153</v>
+        <v>132217338</v>
       </c>
       <c r="B4" t="n">
-        <v>58286</v>
+        <v>97913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +915,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>221944</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Simontorp, Vanderydvattnet, Vg</t>
+          <t>Stora Grankärr, Stora Grankärr, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>342632</v>
+        <v>342425</v>
       </c>
       <c r="R4" t="n">
-        <v>6441273</v>
+        <v>6440968</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
@@ -954,7 +950,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Lilla Edet</t>
+          <t>Ale</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -964,7 +960,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Ale-Skövde</t>
+          <t>Hålanda</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -985,6 +981,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vid kanten av impediment mot vägen...</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132217338</v>
+        <v>132214876</v>
       </c>
       <c r="B5" t="n">
-        <v>97913</v>
+        <v>8444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,33 +1023,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221944</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Grankärr, Stora Grankärr, Vg</t>
+          <t>Sköljeberget, Sköljeberget, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>342425</v>
+        <v>342641</v>
       </c>
       <c r="R5" t="n">
-        <v>6440968</v>
+        <v>6441071</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1087,12 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vid kanten av impediment mot vägen...</t>
+          <t>På död björk i kanten av dråg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132214876</v>
+        <v>132214000</v>
       </c>
       <c r="B6" t="n">
-        <v>8444</v>
+        <v>97919</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,12 +1204,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På död björk i kanten av dråg</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132216998</v>
+        <v>132217153</v>
       </c>
       <c r="B7" t="n">
-        <v>97913</v>
+        <v>58286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,33 +1242,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221944</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Simontorp, Simontorp, Vg</t>
+          <t>Vanderydsv, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>342632</v>
+        <v>342414</v>
       </c>
       <c r="R7" t="n">
-        <v>6441273</v>
+        <v>6440976</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1277,7 +1285,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Lilla Edet</t>
+          <t>Ale</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1287,7 +1295,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Ale-Skövde</t>
+          <t>Hålanda</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1334,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132214000</v>
+        <v>132216998</v>
       </c>
       <c r="B8" t="n">
-        <v>97919</v>
+        <v>97913</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,34 +1353,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sköljeberget, Sköljeberget, Vg</t>
+          <t>Västervatten, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>342641</v>
+        <v>342429</v>
       </c>
       <c r="R8" t="n">
-        <v>6441071</v>
+        <v>6441007</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,6 +1431,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>132217338</v>
       </c>
       <c r="B4" t="n">
-        <v>97954</v>
+        <v>97957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132214000</v>
       </c>
       <c r="B6" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>132217153</v>
       </c>
       <c r="B7" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>132216998</v>
       </c>
       <c r="B8" t="n">
-        <v>97954</v>
+        <v>97957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>132061204</v>
       </c>
       <c r="B3" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>132217338</v>
       </c>
       <c r="B4" t="n">
-        <v>97957</v>
+        <v>97965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132214000</v>
       </c>
       <c r="B6" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>132217153</v>
       </c>
       <c r="B7" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>132216998</v>
       </c>
       <c r="B8" t="n">
-        <v>97957</v>
+        <v>97965</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>132061204</v>
       </c>
       <c r="B3" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>132217338</v>
       </c>
       <c r="B4" t="n">
-        <v>97965</v>
+        <v>97975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132214000</v>
       </c>
       <c r="B6" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>132217153</v>
       </c>
       <c r="B7" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>132216998</v>
       </c>
       <c r="B8" t="n">
-        <v>97965</v>
+        <v>97975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -1345,7 +1345,7 @@
         <v>132216998</v>
       </c>
       <c r="B8" t="n">
-        <v>97975</v>
+        <v>97976</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>132217338</v>
       </c>
       <c r="B4" t="n">
-        <v>97975</v>
+        <v>97977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132214000</v>
       </c>
       <c r="B6" t="n">
-        <v>97981</v>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>132216998</v>
       </c>
       <c r="B8" t="n">
-        <v>97976</v>
+        <v>97977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>132061204</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>132217338</v>
       </c>
       <c r="B4" t="n">
-        <v>97977</v>
+        <v>97978</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132214000</v>
       </c>
       <c r="B6" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>132217153</v>
       </c>
       <c r="B7" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>132216998</v>
       </c>
       <c r="B8" t="n">
-        <v>97977</v>
+        <v>97978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>132217338</v>
       </c>
       <c r="B4" t="n">
-        <v>97978</v>
+        <v>97980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132214000</v>
       </c>
       <c r="B6" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>132216998</v>
       </c>
       <c r="B8" t="n">
-        <v>97978</v>
+        <v>97980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>132217338</v>
       </c>
       <c r="B4" t="n">
-        <v>97980</v>
+        <v>97981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132214000</v>
       </c>
       <c r="B6" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>132216998</v>
       </c>
       <c r="B8" t="n">
-        <v>97980</v>
+        <v>97981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1448,6 +1448,234 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133136349</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58115</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vanderydsvattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>342607</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6441199</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Inspelad i fält på plats med passiv ljudinspelning (Audiomoth)</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133136538</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58677</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vanderydsvattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>342607</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6441199</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Passiv ljudinspelning med Audiomoth 1.2</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -1453,7 +1453,7 @@
         <v>133136349</v>
       </c>
       <c r="B9" t="n">
-        <v>58115</v>
+        <v>58118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>133136538</v>
       </c>
       <c r="B10" t="n">
-        <v>58677</v>
+        <v>58680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -1453,7 +1453,7 @@
         <v>133136349</v>
       </c>
       <c r="B9" t="n">
-        <v>58118</v>
+        <v>58119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>133136538</v>
       </c>
       <c r="B10" t="n">
-        <v>58680</v>
+        <v>58681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132062953</v>
+        <v>132214369</v>
       </c>
       <c r="B2" t="n">
-        <v>8444</v>
+        <v>97863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>2607</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Späd frullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Frullania fragilifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Taylor) Gottsche, Lindenb. &amp; Nees</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sköljeberget, Sköljeberget, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342640</v>
+        <v>342641</v>
       </c>
       <c r="R2" t="n">
-        <v>6441246</v>
+        <v>6441071</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera färska gnagspår på död björk</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,11 +785,11 @@
         <v>132061204</v>
       </c>
       <c r="B3" t="n">
-        <v>57951</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -904,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132217338</v>
+        <v>132217153</v>
       </c>
       <c r="B4" t="n">
-        <v>97981</v>
+        <v>58349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,33 +905,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Grankärr, Stora Grankärr, Vg</t>
+          <t>Vanderydsv, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>342425</v>
+        <v>342414</v>
       </c>
       <c r="R4" t="n">
-        <v>6440968</v>
+        <v>6440976</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,11 +979,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vid kanten av impediment mot vägen...</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,45 +1005,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132214876</v>
+        <v>133136349</v>
       </c>
       <c r="B5" t="n">
-        <v>8444</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sköljeberget, Sköljeberget, Vg</t>
+          <t>Vanderydsvattnet, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>342641</v>
+        <v>342607</v>
       </c>
       <c r="R5" t="n">
-        <v>6441071</v>
+        <v>6441199</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,27 +1078,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På död björk i kanten av dråg</t>
+          <t>Inspelad i fält på plats med passiv ljudinspelning (Audiomoth)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,45 +1115,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132214000</v>
+        <v>133136538</v>
       </c>
       <c r="B6" t="n">
-        <v>97987</v>
+        <v>58698</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sköljeberget, Sköljeberget, Vg</t>
+          <t>Vanderydsvattnet, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>342641</v>
+        <v>342607</v>
       </c>
       <c r="R6" t="n">
-        <v>6441071</v>
+        <v>6441199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,22 +1185,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Passiv ljudinspelning med Audiomoth 1.2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,6 +1214,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1231,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132217153</v>
+        <v>132062953</v>
       </c>
       <c r="B7" t="n">
-        <v>58328</v>
+        <v>8449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,41 +1244,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vanderydsv, Vg</t>
+          <t>Sköljeberget, Sköljeberget, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>342414</v>
+        <v>342640</v>
       </c>
       <c r="R7" t="n">
-        <v>6440976</v>
+        <v>6441246</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,22 +1303,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera färska gnagspår på död björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132216998</v>
+        <v>132214876</v>
       </c>
       <c r="B8" t="n">
-        <v>97981</v>
+        <v>8449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,34 +1361,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221944</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västervatten, Vg</t>
+          <t>Sköljeberget, Sköljeberget, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>342429</v>
+        <v>342641</v>
       </c>
       <c r="R8" t="n">
-        <v>6441007</v>
+        <v>6441071</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1430,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På död björk i kanten av dråg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,7 +1444,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1450,53 +1462,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133136349</v>
+        <v>132216998</v>
       </c>
       <c r="B9" t="n">
-        <v>58119</v>
+        <v>98054</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>221944</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vanderydsvattnet, Vg</t>
+          <t>Västervatten, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>342607</v>
+        <v>342429</v>
       </c>
       <c r="R9" t="n">
-        <v>6441199</v>
+        <v>6441007</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,17 +1527,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Inspelad i fält på plats med passiv ljudinspelning (Audiomoth)</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,6 +1551,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1560,53 +1570,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133136538</v>
+        <v>132217338</v>
       </c>
       <c r="B10" t="n">
-        <v>58681</v>
+        <v>98054</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103055</v>
+        <v>221944</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vanderydsvattnet, Vg</t>
+          <t>Stora Grankärr, Stora Grankärr, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>342607</v>
+        <v>342425</v>
       </c>
       <c r="R10" t="n">
-        <v>6441199</v>
+        <v>6440968</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,27 +1631,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Passiv ljudinspelning med Audiomoth 1.2</t>
+          <t>Vid kanten av impediment mot vägen...</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,7 +1660,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1675,6 +1675,113 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132214000</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sköljeberget, Sköljeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>342641</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6441071</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15890-2026 artfynd.xlsx
+++ b/artfynd/A 15890-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132214369</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132061204</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132217153</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133136349</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133136538</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132062953</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132214876</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132216998</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132217338</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,8 +1832,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132214000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>